--- a/gamingPCFunds.xlsx
+++ b/gamingPCFunds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taylo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF15AB9-972B-4A5E-8B54-25387C96358E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3A8E3D-49FD-48FC-9C2B-AF05E0249DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5738C114-AE19-4C2E-908A-C52CB70B23BC}"/>
+    <workbookView xWindow="-28920" yWindow="-3210" windowWidth="29040" windowHeight="15720" xr2:uid="{5738C114-AE19-4C2E-908A-C52CB70B23BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,12 +119,6 @@
     <t>% SAVED</t>
   </si>
   <si>
-    <t>Asus TUF GAMING B650-E WIFI</t>
-  </si>
-  <si>
-    <t>PowerColor Reaper AMD Radeon RX 9070 16GB GDDR6</t>
-  </si>
-  <si>
     <t>Lexar DDR5 RAM 32GB Kit (2x16GB)</t>
   </si>
   <si>
@@ -158,13 +152,19 @@
     <t>AMD Ryzen 7 7700X</t>
   </si>
   <si>
-    <t>Fikwot FX991 1TB SSD, M.2</t>
-  </si>
-  <si>
     <t>CORSAIR RM750e (2025)</t>
   </si>
   <si>
-    <t>OS to use: CachyOS Hyprland Noctalia</t>
+    <t>MSI PRO B850-S WIFI 6E</t>
+  </si>
+  <si>
+    <t>Crucial P310 2TB SSD M.2</t>
+  </si>
+  <si>
+    <t>OS to use: CachyOS Cosmic</t>
+  </si>
+  <si>
+    <t>Sapphire technology Pure AMD Radeon RX 9060 XT</t>
   </si>
 </sst>
 </file>
@@ -700,6 +700,9 @@
                 <c:pt idx="8">
                   <c:v>46317</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46318</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -735,6 +738,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>416.81</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>417.71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2960,26 +2966,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BAD8EC0-6FDB-49E6-86B8-06EF65E9F4AD}">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" customWidth="1"/>
+    <col min="17" max="17" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="27" t="s">
         <v>0</v>
@@ -3006,7 +3012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="3">
         <v>46296</v>
@@ -3018,11 +3024,11 @@
         <v>0</v>
       </c>
       <c r="E3" s="32">
-        <f t="shared" ref="E3:E37" si="0">SUM(C3,D3)</f>
+        <f t="shared" ref="E3:E12" si="0">SUM(C3,D3)</f>
         <v>350.65</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H3" s="21">
         <v>192.83</v>
@@ -3034,7 +3040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="3">
         <v>46299</v>
@@ -3050,10 +3056,10 @@
         <v>353.2</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H4" s="22">
-        <v>629.99</v>
+        <v>529.99</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>6</v>
@@ -3062,7 +3068,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="3">
         <v>46306</v>
@@ -3078,7 +3084,7 @@
         <v>363.2</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H5" s="22">
         <v>419.99</v>
@@ -3090,7 +3096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="3">
         <v>46307</v>
@@ -3109,7 +3115,7 @@
         <v>40</v>
       </c>
       <c r="H6" s="22">
-        <v>145.99</v>
+        <v>229.99</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>6</v>
@@ -3118,7 +3124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="3">
         <v>46308</v>
@@ -3134,7 +3140,7 @@
         <v>365.23999999999995</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H7" s="22">
         <v>104.99</v>
@@ -3146,7 +3152,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="3">
         <v>46309</v>
@@ -3162,7 +3168,7 @@
         <v>365.4</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H8" s="22">
         <v>27.9</v>
@@ -3174,7 +3180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="3">
         <v>46311</v>
@@ -3190,7 +3196,7 @@
         <v>366.46</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H9" s="22">
         <v>69.989999999999995</v>
@@ -3202,7 +3208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="3">
         <v>46314</v>
@@ -3218,10 +3224,10 @@
         <v>416.46</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H10" s="22">
-        <v>158.05000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>6</v>
@@ -3230,7 +3236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="3">
         <v>46317</v>
@@ -3246,26 +3252,35 @@
         <v>416.81</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H11" s="22">
         <v>215.18</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J11" s="17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="55"/>
+      <c r="B12" s="3">
+        <v>46318</v>
+      </c>
+      <c r="C12" s="28">
+        <v>401.07</v>
+      </c>
+      <c r="D12" s="28">
+        <v>16.64</v>
+      </c>
+      <c r="E12" s="55">
+        <f t="shared" si="0"/>
+        <v>417.71</v>
+      </c>
       <c r="G12" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H12" s="22">
         <v>34.99</v>
@@ -3277,7 +3292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="3"/>
       <c r="C13" s="28"/>
@@ -3296,7 +3311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="3"/>
       <c r="C14" s="28"/>
@@ -3307,10 +3322,10 @@
       </c>
       <c r="H14" s="54">
         <f>SUM(H3:H13)</f>
-        <v>2138.9</v>
+        <v>2084.84</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="3"/>
       <c r="C15" s="28"/>
@@ -3319,7 +3334,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="3"/>
       <c r="C16" s="28"/>
@@ -3330,10 +3345,10 @@
       </c>
       <c r="H16" s="24">
         <f>MAX(E3:E37)</f>
-        <v>416.81</v>
+        <v>417.71</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="3"/>
       <c r="C17" s="28"/>
@@ -3344,10 +3359,10 @@
       </c>
       <c r="H17" s="52">
         <f>H16/H14</f>
-        <v>0.19487119547430923</v>
+        <v>0.20035590261123154</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="3"/>
       <c r="C18" s="28"/>
@@ -3358,10 +3373,10 @@
       </c>
       <c r="H18" s="25" t="str">
         <f>IMSUB(H14,H16)</f>
-        <v>1722.09</v>
+        <v>1667.13</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="3"/>
       <c r="C19" s="28"/>
@@ -3371,7 +3386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="3"/>
       <c r="C20" s="28"/>
@@ -3381,7 +3396,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="3"/>
       <c r="C21" s="28"/>
@@ -3391,7 +3406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="3"/>
       <c r="C22" s="28"/>
@@ -3402,37 +3417,37 @@
       </c>
       <c r="I22" s="53"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="3"/>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
       <c r="E23" s="55"/>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="3"/>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
       <c r="E24" s="55"/>
       <c r="Q24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="3"/>
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
       <c r="E25" s="55"/>
       <c r="Q25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="3"/>
       <c r="C26" s="28"/>
@@ -3457,10 +3472,10 @@
         <v>24</v>
       </c>
       <c r="Q26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="3"/>
       <c r="C27" s="28"/>
@@ -3485,10 +3500,10 @@
         <v>13</v>
       </c>
       <c r="Q27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="3"/>
       <c r="C28" s="28"/>
@@ -3511,7 +3526,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="3"/>
       <c r="C29" s="28"/>
@@ -3529,7 +3544,7 @@
         <v>44.49</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="3"/>
       <c r="C30" s="28"/>
@@ -3540,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="3"/>
       <c r="C31" s="28"/>
@@ -3558,7 +3573,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="3"/>
       <c r="C32" s="28"/>
@@ -3576,7 +3591,7 @@
         <v>4.4953922229714542E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="3"/>
       <c r="C33" s="28"/>
@@ -3594,7 +3609,7 @@
         <v>44.47</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="3"/>
       <c r="C34" s="28"/>
@@ -3605,7 +3620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="3"/>
       <c r="C35" s="28"/>
@@ -3616,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="3"/>
       <c r="C36" s="28"/>
@@ -3627,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="3"/>
       <c r="C37" s="28"/>
